--- a/teacher/tracker-alevel-pure.xlsx
+++ b/teacher/tracker-alevel-pure.xlsx
@@ -157,7 +157,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -188,6 +188,42 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="001B998B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0392B"/>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4A93F"/>
+          <bgColor rgb="FFF4A93F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1B998B"/>
+          <bgColor rgb="FF1B998B"/>
         </patternFill>
       </fill>
     </dxf>
@@ -841,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1228,13 +1264,13 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:H27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1253,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1550,13 +1586,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1575,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2052,13 +2088,13 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:K27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2077,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2404,13 +2440,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2429,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2756,13 +2792,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2781,7 +2817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3168,13 +3204,13 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:H27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3193,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3610,13 +3646,13 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:I27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3635,7 +3671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3902,13 +3938,13 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:D27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3927,7 +3963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4254,13 +4290,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4279,7 +4315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4576,13 +4612,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:E27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4601,7 +4637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4958,13 +4994,13 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:G27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4983,7 +5019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5310,13 +5346,13 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:F27">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3" stopIfTrue="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4" stopIfTrue="0">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5" stopIfTrue="0">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
